--- a/football/data/balanced_unbalanced_stake_tracker.xlsx
+++ b/football/data/balanced_unbalanced_stake_tracker.xlsx
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V17"/>
+  <dimension ref="A1:X17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="19.44140625" customWidth="1" min="1" max="1"/>
@@ -585,6 +585,16 @@
           <t>Accumulated Profit (GHS)</t>
         </is>
       </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Opportunity ID</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1105,10 +1115,6 @@
       <c r="N17" t="n">
         <v>13.32</v>
       </c>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
         <v>1000</v>
       </c>
@@ -1118,7 +1124,6 @@
       <c r="U17" t="n">
         <v>65.61</v>
       </c>
-      <c r="V17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
